--- a/Entregas.xlsx
+++ b/Entregas.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/78f04a1edbdcd847/Documentos/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/78f04a1edbdcd847/Documentos/Bases/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="8_{B5C97DAB-BDBF-4125-B8A5-F45CB503AB53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1908A962-65AB-4D7E-900C-3B00BA7EFA47}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="8_{B5C97DAB-BDBF-4125-B8A5-F45CB503AB53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D6B784F-CE28-42D9-AD26-74F00974ED14}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{11CB4283-0386-44E0-AF73-975A4BE33354}"/>
   </bookViews>
@@ -59,12 +59,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>Paack</t>
-  </si>
-  <si>
-    <t>Ecoscoting</t>
   </si>
   <si>
     <t>Data</t>
@@ -77,6 +74,12 @@
   </si>
   <si>
     <t>5/27/2026</t>
+  </si>
+  <si>
+    <t>5/29/2026</t>
+  </si>
+  <si>
+    <t>Ecoscouting</t>
   </si>
 </sst>
 </file>
@@ -100,7 +103,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -168,11 +171,31 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -199,6 +222,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -214,6 +245,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -513,24 +548,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2078E04-C73F-4A4B-8DED-06D8C7D96342}">
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.42578125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1" spans="1:3" s="12" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
+      <c r="C1" s="13" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -685,7 +720,7 @@
     </row>
     <row r="16" spans="1:3" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B16" s="7"/>
       <c r="C16" s="8">
@@ -694,7 +729,7 @@
     </row>
     <row r="17" spans="1:3" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="9" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B17" s="3">
         <v>15</v>
@@ -705,7 +740,7 @@
     </row>
     <row r="18" spans="1:3" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B18" s="3">
         <v>8</v>
@@ -714,7 +749,18 @@
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="19" spans="1:3" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B19" s="11">
+        <v>18</v>
+      </c>
+      <c r="C19" s="10">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/Entregas.xlsx
+++ b/Entregas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/78f04a1edbdcd847/Documentos/Bases/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17" documentId="8_{B5C97DAB-BDBF-4125-B8A5-F45CB503AB53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D6B784F-CE28-42D9-AD26-74F00974ED14}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="8_{B5C97DAB-BDBF-4125-B8A5-F45CB503AB53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2FCACF44-A14C-445C-99EB-2D252C6E8612}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{11CB4283-0386-44E0-AF73-975A4BE33354}"/>
   </bookViews>
@@ -195,7 +195,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -222,14 +222,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -548,7 +556,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2078E04-C73F-4A4B-8DED-06D8C7D96342}">
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -557,14 +565,14 @@
     <col min="15" max="15" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="12" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>6</v>
       </c>
     </row>
@@ -760,7 +768,18 @@
         <v>28</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="20" spans="1:3" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="13">
+        <v>46028</v>
+      </c>
+      <c r="B20" s="14">
+        <v>9</v>
+      </c>
+      <c r="C20" s="15">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/Entregas.xlsx
+++ b/Entregas.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/78f04a1edbdcd847/Documentos/Bases/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="25" documentId="8_{B5C97DAB-BDBF-4125-B8A5-F45CB503AB53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2FCACF44-A14C-445C-99EB-2D252C6E8612}"/>
+  <xr:revisionPtr revIDLastSave="27" documentId="8_{B5C97DAB-BDBF-4125-B8A5-F45CB503AB53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BC3545C1-628A-4250-8816-1BB8F127DA7D}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{11CB4283-0386-44E0-AF73-975A4BE33354}"/>
   </bookViews>
@@ -195,7 +195,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -230,12 +230,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -770,12 +764,12 @@
     </row>
     <row r="20" spans="1:3" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="13">
-        <v>46028</v>
-      </c>
-      <c r="B20" s="14">
+        <v>46174</v>
+      </c>
+      <c r="B20" s="11">
         <v>9</v>
       </c>
-      <c r="C20" s="15">
+      <c r="C20" s="10">
         <v>52</v>
       </c>
     </row>
